--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Dharmapuri.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Dharmapuri.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dex\Desktop\TN WP 2026-27\SL 2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0670AE4-5F30-4676-9877-1376888B47D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B11271-5C4F-43FD-8D7E-80386B622EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>PADDY</t>
   </si>
   <si>
-    <t>COTTON</t>
-  </si>
-  <si>
     <t>SUGAR   CANE</t>
   </si>
   <si>
@@ -493,6 +490,9 @@
   </si>
   <si>
     <t>@ A Group # B Group Village</t>
+  </si>
+  <si>
+    <t>COTTON (K)</t>
   </si>
 </sst>
 </file>
@@ -808,6 +808,12 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -819,12 +825,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="3" spans="1:12" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="47"/>
       <c r="C3" s="47"/>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="4" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
@@ -1249,7 +1249,7 @@
       <c r="H4" s="48"/>
       <c r="I4" s="48"/>
       <c r="J4" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K4" s="48"/>
       <c r="L4" s="48"/>
@@ -1259,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="53" t="s">
         <v>6</v>
@@ -1319,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4">
         <v>8</v>
@@ -1331,10 +1331,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>62</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>63</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="4">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4">
         <v>10</v>
@@ -1410,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4">
         <v>1</v>
@@ -1433,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4">
         <v>4</v>
@@ -1448,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H10" s="4">
         <v>1</v>
@@ -1471,7 +1471,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="4">
         <v>8</v>
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
@@ -1509,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="4">
         <v>8</v>
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
@@ -1533,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -1547,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4">
         <v>20</v>
@@ -1562,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H13" s="4">
         <v>6</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K13" s="21">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4">
         <v>14</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H14" s="4">
         <v>5</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="4">
         <v>8</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H15" s="4">
         <v>2</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="28">
         <v>8</v>
@@ -1688,7 +1688,7 @@
         <v>6</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L16" s="4">
         <v>7</v>
@@ -1699,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="28">
         <v>8</v>
@@ -1737,7 +1737,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="28">
         <v>20</v>
@@ -1761,10 +1761,10 @@
         <v>1</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L18" s="4">
         <v>21</v>
@@ -3331,297 +3331,297 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
     </row>
     <row r="2" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
     </row>
     <row r="3" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
+      <c r="A3" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
+      <c r="G3" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="45" t="s">
+      <c r="Q3" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+    </row>
+    <row r="4" spans="1:22" ht="40.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-    </row>
-    <row r="4" spans="1:22" ht="39.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="I4" s="43"/>
+      <c r="J4" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="K4" s="43"/>
+      <c r="L4" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41" t="s">
+      <c r="M4" s="44"/>
+      <c r="N4" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="44"/>
+      <c r="P4" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41" t="s">
+      <c r="S4" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="T4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="42"/>
-      <c r="P4" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="T4" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42" t="s">
+    </row>
+    <row r="5" spans="1:22" ht="27.2" x14ac:dyDescent="0.2">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="27.2" x14ac:dyDescent="0.2">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="44"/>
+    </row>
+    <row r="6" spans="1:22" s="13" customFormat="1" ht="25.85" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5" s="42"/>
-    </row>
-    <row r="6" spans="1:22" s="13" customFormat="1" ht="25.85" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R6" s="12"/>
       <c r="S6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="T6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="U6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="T6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="U6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="V6" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="22.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-    </row>
-    <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+    </row>
+    <row r="8" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>77</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -3635,7 +3635,7 @@
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
       <c r="P8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -3644,16 +3644,16 @@
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
     </row>
-    <row r="9" spans="1:22" ht="23.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -3665,22 +3665,22 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
       <c r="R9" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
     </row>
-    <row r="10" spans="1:22" ht="23.3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="33"/>
       <c r="C10" s="11"/>
@@ -3694,13 +3694,13 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
@@ -3708,17 +3708,17 @@
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
     </row>
-    <row r="11" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -3732,48 +3732,48 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R11" s="11"/>
       <c r="S11" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
     </row>
-    <row r="12" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-    </row>
-    <row r="13" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
+      <c r="A12" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+    </row>
+    <row r="13" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -3782,7 +3782,7 @@
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -3798,12 +3798,12 @@
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
     </row>
-    <row r="14" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>87</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>88</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -3812,7 +3812,7 @@
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -3824,18 +3824,18 @@
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
     </row>
-    <row r="15" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -3844,11 +3844,11 @@
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
@@ -3862,12 +3862,12 @@
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
     </row>
-    <row r="16" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A16" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>92</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>93</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -3884,22 +3884,22 @@
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -3915,7 +3915,7 @@
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
       <c r="P17" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
@@ -3924,12 +3924,12 @@
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
     </row>
-    <row r="18" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>96</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>97</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -3942,7 +3942,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
@@ -3954,19 +3954,19 @@
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
     </row>
-    <row r="19" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
@@ -3979,26 +3979,26 @@
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S19" s="11"/>
       <c r="T19" s="11"/>
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
     </row>
-    <row r="20" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A20" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -4016,12 +4016,12 @@
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
-    <row r="21" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A21" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -4040,18 +4040,18 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
       <c r="S21" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T21" s="11"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
-    <row r="22" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -4070,18 +4070,18 @@
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
       <c r="S22" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T22" s="15"/>
       <c r="U22" s="15"/>
       <c r="V22" s="15"/>
     </row>
-    <row r="23" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -4100,18 +4100,18 @@
       <c r="Q23" s="17"/>
       <c r="R23" s="17"/>
       <c r="S23" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
       <c r="V23" s="17"/>
     </row>
-    <row r="24" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -4130,20 +4130,20 @@
       <c r="Q24" s="17"/>
       <c r="R24" s="17"/>
       <c r="S24" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
       <c r="V24" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
+      <c r="A25" s="16" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
-        <v>84</v>
-      </c>
       <c r="B25" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -4162,18 +4162,18 @@
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
       <c r="V25" s="17"/>
     </row>
-    <row r="26" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -4184,7 +4184,7 @@
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
@@ -4198,12 +4198,12 @@
       <c r="U26" s="17"/>
       <c r="V26" s="17"/>
     </row>
-    <row r="27" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -4214,7 +4214,7 @@
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -4228,12 +4228,12 @@
       <c r="U27" s="17"/>
       <c r="V27" s="17"/>
     </row>
-    <row r="28" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -4244,7 +4244,7 @@
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
       <c r="K28" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
@@ -4258,12 +4258,12 @@
       <c r="U28" s="17"/>
       <c r="V28" s="17"/>
     </row>
-    <row r="29" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -4274,7 +4274,7 @@
       <c r="I29" s="17"/>
       <c r="J29" s="17"/>
       <c r="K29" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
@@ -4288,12 +4288,12 @@
       <c r="U29" s="17"/>
       <c r="V29" s="17"/>
     </row>
-    <row r="30" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -4315,20 +4315,20 @@
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
       <c r="V30" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -4339,7 +4339,7 @@
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
@@ -4350,12 +4350,12 @@
       <c r="U31" s="15"/>
       <c r="V31" s="15"/>
     </row>
-    <row r="32" spans="1:22" ht="17.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -4373,19 +4373,19 @@
       <c r="P32" s="17"/>
       <c r="Q32" s="17"/>
       <c r="R32" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S32" s="17"/>
       <c r="T32" s="17"/>
       <c r="U32" s="17"/>
       <c r="V32" s="17"/>
     </row>
-    <row r="33" spans="1:22" ht="18.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -4403,19 +4403,19 @@
       <c r="P33" s="17"/>
       <c r="Q33" s="17"/>
       <c r="R33" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S33" s="17"/>
       <c r="T33" s="17"/>
       <c r="U33" s="17"/>
       <c r="V33" s="17"/>
     </row>
-    <row r="34" spans="1:22" ht="19.55" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -4433,17 +4433,17 @@
       <c r="P34" s="17"/>
       <c r="Q34" s="17"/>
       <c r="R34" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
       <c r="U34" s="17"/>
       <c r="V34" s="17"/>
     </row>
-    <row r="35" spans="1:22" ht="19.55" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A35" s="14"/>
       <c r="B35" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
@@ -4466,9 +4466,9 @@
       <c r="U35" s="24"/>
       <c r="V35" s="24"/>
     </row>
-    <row r="36" spans="1:22" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A36" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="36"/>
       <c r="C36" s="37"/>
@@ -4487,24 +4487,19 @@
       <c r="P36" s="35"/>
       <c r="Q36" s="36"/>
       <c r="R36" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S36" s="9"/>
       <c r="T36" s="9"/>
       <c r="U36" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:V3"/>
     <mergeCell ref="A7:V7"/>
     <mergeCell ref="A12:V12"/>
     <mergeCell ref="J4:K4"/>
@@ -4518,6 +4513,11 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:V3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K15" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -6058,254 +6058,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
     </row>
     <row r="2" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
     </row>
     <row r="3" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
+      <c r="A3" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
+      <c r="G3" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
+      <c r="Q3" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
     </row>
     <row r="4" spans="1:21" ht="40.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41" t="s">
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="43"/>
+      <c r="L4" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="O4" s="44"/>
+      <c r="P4" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="42" t="s">
+      <c r="Q4" s="46"/>
+      <c r="R4" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="S4" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="O4" s="42"/>
-      <c r="P4" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="S4" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="5" spans="1:21" ht="27.2" x14ac:dyDescent="0.2">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="44"/>
+    </row>
+    <row r="6" spans="1:21" s="13" customFormat="1" ht="38.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="U5" s="42"/>
-    </row>
-    <row r="6" spans="1:21" s="13" customFormat="1" ht="38.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U6" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A7" s="57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -6328,16 +6328,16 @@
       <c r="T7" s="58"/>
       <c r="U7" s="58"/>
     </row>
-    <row r="8" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>126</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -6346,7 +6346,7 @@
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
@@ -6354,23 +6354,23 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
     </row>
-    <row r="9" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>129</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>130</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -6389,15 +6389,15 @@
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -6406,7 +6406,7 @@
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -6421,12 +6421,12 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
     </row>
-    <row r="11" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -6435,7 +6435,7 @@
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -6446,25 +6446,25 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
     </row>
-    <row r="12" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -6472,27 +6472,27 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S12" s="11"/>
       <c r="T12" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U12" s="11"/>
     </row>
-    <row r="13" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>135</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>136</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -6510,18 +6510,18 @@
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
     </row>
-    <row r="14" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -6532,7 +6532,7 @@
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
@@ -6543,16 +6543,16 @@
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
       <c r="T14" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U14" s="11"/>
     </row>
-    <row r="15" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -6566,7 +6566,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
       <c r="N15" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -6574,43 +6574,43 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-    </row>
-    <row r="17" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
+      <c r="A16" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+    </row>
+    <row r="17" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -6627,19 +6627,19 @@
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
       <c r="T17" s="15"/>
       <c r="U17" s="15"/>
     </row>
-    <row r="18" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -6652,7 +6652,7 @@
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
@@ -6663,19 +6663,19 @@
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
     </row>
-    <row r="19" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -6692,17 +6692,17 @@
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
     </row>
-    <row r="20" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
@@ -6721,17 +6721,17 @@
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
     </row>
-    <row r="21" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
@@ -6742,7 +6742,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
@@ -6752,12 +6752,12 @@
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
     </row>
-    <row r="22" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="13.6" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -6777,14 +6777,14 @@
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
       <c r="T22" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U22" s="17"/>
     </row>
-    <row r="23" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="14.3" x14ac:dyDescent="0.2">
       <c r="A23" s="14"/>
       <c r="B23" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
@@ -6829,9 +6829,9 @@
       <c r="T24" s="59"/>
       <c r="U24" s="59"/>
     </row>
-    <row r="25" spans="1:21" ht="14.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="39"/>
       <c r="C25" s="40"/>
@@ -6847,24 +6847,19 @@
       <c r="M25" s="38"/>
       <c r="N25" s="38"/>
       <c r="O25" s="56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P25" s="56"/>
       <c r="Q25" s="56"/>
       <c r="R25" s="56"/>
       <c r="S25" s="56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T25" s="56"/>
       <c r="U25" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:U3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
@@ -6881,6 +6876,11 @@
     <mergeCell ref="U4:U5"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="O25:R25"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K8" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
